--- a/backend/График_дежурств.xlsx
+++ b/backend/График_дежурств.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\denis\Downloads\практика\schedule-app\backend\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\denis\Downloads\Загрузки\Загрузки\практика\schedule-app\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D0F8E4-6471-4D6B-8877-E421D350ABE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3EE6D4-3807-4745-AB13-FE7459BE2135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="10690" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="сессия_зима" sheetId="2" r:id="rId1"/>
@@ -1504,18 +1504,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H307"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.7265625" style="109" customWidth="1"/>
-    <col min="2" max="2" width="4.7265625" style="110" customWidth="1"/>
+    <col min="1" max="1" width="4.77734375" style="109" customWidth="1"/>
+    <col min="2" max="2" width="4.77734375" style="110" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="6" width="18.26953125" customWidth="1"/>
-    <col min="7" max="7" width="6.81640625" customWidth="1"/>
-    <col min="8" max="8" width="5.7265625" customWidth="1"/>
+    <col min="5" max="6" width="18.21875" customWidth="1"/>
+    <col min="7" max="7" width="6.77734375" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="33.5" thickBot="1">
+    <row r="1" spans="1:8" ht="33.6" thickBot="1">
       <c r="A1" s="45" t="s">
         <v>28</v>
       </c>
@@ -1539,7 +1539,7 @@
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="112">
-        <v>44917</v>
+        <v>46013</v>
       </c>
       <c r="B2" s="115" t="s">
         <v>5</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="112">
-        <v>44918</v>
+        <v>46014</v>
       </c>
       <c r="B10" s="115" t="s">
         <v>20</v>
@@ -1711,7 +1711,7 @@
       <c r="G12" s="56"/>
       <c r="H12" s="69"/>
     </row>
-    <row r="13" spans="1:8" ht="15.5">
+    <row r="13" spans="1:8" ht="15.6">
       <c r="A13" s="113"/>
       <c r="B13" s="116"/>
       <c r="C13" s="52">
@@ -1729,7 +1729,7 @@
       <c r="G13" s="70"/>
       <c r="H13" s="71"/>
     </row>
-    <row r="14" spans="1:8" ht="15.5">
+    <row r="14" spans="1:8" ht="15.6">
       <c r="A14" s="113"/>
       <c r="B14" s="116"/>
       <c r="C14" s="52">
@@ -1745,7 +1745,7 @@
       <c r="G14" s="70"/>
       <c r="H14" s="71"/>
     </row>
-    <row r="15" spans="1:8" ht="15.5">
+    <row r="15" spans="1:8" ht="15.6">
       <c r="A15" s="113"/>
       <c r="B15" s="116"/>
       <c r="C15" s="52">
@@ -1793,7 +1793,7 @@
     </row>
     <row r="18" spans="1:8" ht="30" customHeight="1">
       <c r="A18" s="112">
-        <v>44919</v>
+        <v>46015</v>
       </c>
       <c r="B18" s="115" t="s">
         <v>21</v>
@@ -1825,7 +1825,7 @@
       <c r="G19" s="56"/>
       <c r="H19" s="69"/>
     </row>
-    <row r="20" spans="1:8" ht="15.5">
+    <row r="20" spans="1:8" ht="15.6">
       <c r="A20" s="113"/>
       <c r="B20" s="116"/>
       <c r="C20" s="52">
@@ -1843,7 +1843,7 @@
       <c r="G20" s="70"/>
       <c r="H20" s="71"/>
     </row>
-    <row r="21" spans="1:8" ht="15.5">
+    <row r="21" spans="1:8" ht="15.6">
       <c r="A21" s="113"/>
       <c r="B21" s="116"/>
       <c r="C21" s="52">
@@ -1861,7 +1861,7 @@
       <c r="G21" s="70"/>
       <c r="H21" s="71"/>
     </row>
-    <row r="22" spans="1:8" ht="15.5">
+    <row r="22" spans="1:8" ht="15.6">
       <c r="A22" s="113"/>
       <c r="B22" s="116"/>
       <c r="C22" s="52">
@@ -1877,7 +1877,7 @@
       <c r="G22" s="70"/>
       <c r="H22" s="71"/>
     </row>
-    <row r="23" spans="1:8" ht="15.5">
+    <row r="23" spans="1:8" ht="15.6">
       <c r="A23" s="113"/>
       <c r="B23" s="116"/>
       <c r="C23" s="52">
@@ -1923,7 +1923,7 @@
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1">
       <c r="A26" s="112">
-        <v>44920</v>
+        <v>46016</v>
       </c>
       <c r="B26" s="115" t="s">
         <v>24</v>
@@ -1955,7 +1955,7 @@
       <c r="G27" s="56"/>
       <c r="H27" s="69"/>
     </row>
-    <row r="28" spans="1:8" ht="15.5">
+    <row r="28" spans="1:8" ht="15.6">
       <c r="A28" s="113"/>
       <c r="B28" s="116"/>
       <c r="C28" s="52">
@@ -1971,7 +1971,7 @@
       <c r="G28" s="70"/>
       <c r="H28" s="69"/>
     </row>
-    <row r="29" spans="1:8" ht="15.5">
+    <row r="29" spans="1:8" ht="15.6">
       <c r="A29" s="113"/>
       <c r="B29" s="116"/>
       <c r="C29" s="52">
@@ -1987,7 +1987,7 @@
       <c r="G29" s="70"/>
       <c r="H29" s="71"/>
     </row>
-    <row r="30" spans="1:8" ht="15.5">
+    <row r="30" spans="1:8" ht="15.6">
       <c r="A30" s="113"/>
       <c r="B30" s="116"/>
       <c r="C30" s="52">
@@ -2003,7 +2003,7 @@
       <c r="G30" s="70"/>
       <c r="H30" s="71"/>
     </row>
-    <row r="31" spans="1:8" ht="15.5">
+    <row r="31" spans="1:8" ht="15.6">
       <c r="A31" s="113"/>
       <c r="B31" s="116"/>
       <c r="C31" s="52">
@@ -2019,7 +2019,7 @@
       <c r="G31" s="70"/>
       <c r="H31" s="71"/>
     </row>
-    <row r="32" spans="1:8" ht="15.5">
+    <row r="32" spans="1:8" ht="15.6">
       <c r="A32" s="113"/>
       <c r="B32" s="116"/>
       <c r="C32" s="52">
@@ -2051,7 +2051,7 @@
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1">
       <c r="A34" s="112">
-        <v>44921</v>
+        <v>46017</v>
       </c>
       <c r="B34" s="115" t="s">
         <v>26</v>
@@ -2081,7 +2081,7 @@
       <c r="F35" s="75"/>
       <c r="G35" s="56"/>
     </row>
-    <row r="36" spans="1:8" ht="15.5">
+    <row r="36" spans="1:8" ht="15.6">
       <c r="A36" s="113"/>
       <c r="B36" s="116"/>
       <c r="C36" s="52">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="G36" s="70"/>
     </row>
-    <row r="37" spans="1:8" ht="15.5">
+    <row r="37" spans="1:8" ht="15.6">
       <c r="A37" s="113"/>
       <c r="B37" s="116"/>
       <c r="C37" s="52">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="G37" s="70"/>
     </row>
-    <row r="38" spans="1:8" ht="15.5">
+    <row r="38" spans="1:8" ht="15.6">
       <c r="A38" s="113"/>
       <c r="B38" s="116"/>
       <c r="C38" s="52">
@@ -2130,7 +2130,7 @@
       <c r="F38" s="57"/>
       <c r="G38" s="70"/>
     </row>
-    <row r="39" spans="1:8" ht="15.5">
+    <row r="39" spans="1:8" ht="15.6">
       <c r="A39" s="113"/>
       <c r="B39" s="116"/>
       <c r="C39" s="52">
@@ -2146,7 +2146,7 @@
       <c r="G39" s="70"/>
       <c r="H39" s="71"/>
     </row>
-    <row r="40" spans="1:8" ht="15.5">
+    <row r="40" spans="1:8" ht="15.6">
       <c r="A40" s="113"/>
       <c r="B40" s="116"/>
       <c r="C40" s="52">
@@ -2178,7 +2178,7 @@
     </row>
     <row r="42" spans="1:8" ht="15.75" customHeight="1">
       <c r="A42" s="112">
-        <v>44922</v>
+        <v>46018</v>
       </c>
       <c r="B42" s="115" t="s">
         <v>27</v>
@@ -2298,7 +2298,7 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="112">
-        <v>44923</v>
+        <v>46019</v>
       </c>
       <c r="B50" s="115" t="s">
         <v>33</v>
@@ -2416,7 +2416,7 @@
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1">
       <c r="A58" s="112">
-        <v>44924</v>
+        <v>46020</v>
       </c>
       <c r="B58" s="115" t="s">
         <v>5</v>
@@ -2541,7 +2541,7 @@
     </row>
     <row r="66" spans="1:7" ht="15" customHeight="1">
       <c r="A66" s="112">
-        <v>44925</v>
+        <v>46021</v>
       </c>
       <c r="B66" s="115" t="s">
         <v>20</v>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="G76" s="56"/>
     </row>
-    <row r="77" spans="1:7" ht="15.5">
+    <row r="77" spans="1:7" ht="15.6">
       <c r="A77" s="113"/>
       <c r="B77" s="116"/>
       <c r="C77" s="52">
@@ -3200,7 +3200,7 @@
       <c r="F108" s="54"/>
       <c r="G108" s="56"/>
     </row>
-    <row r="109" spans="1:7" ht="15.5">
+    <row r="109" spans="1:7" ht="15.6">
       <c r="A109" s="113"/>
       <c r="B109" s="116"/>
       <c r="C109" s="52">
@@ -3641,7 +3641,7 @@
       <c r="F139" s="57"/>
       <c r="G139" s="56"/>
     </row>
-    <row r="140" spans="1:7" ht="15.5">
+    <row r="140" spans="1:7" ht="15.6">
       <c r="A140" s="113"/>
       <c r="B140" s="116"/>
       <c r="C140" s="52">
@@ -3656,7 +3656,7 @@
       <c r="F140" s="68"/>
       <c r="G140" s="70"/>
     </row>
-    <row r="141" spans="1:7" ht="15.5">
+    <row r="141" spans="1:7" ht="15.6">
       <c r="A141" s="113"/>
       <c r="B141" s="116"/>
       <c r="C141" s="52">
@@ -3671,7 +3671,7 @@
       <c r="F141" s="68"/>
       <c r="G141" s="70"/>
     </row>
-    <row r="142" spans="1:7" ht="15.5">
+    <row r="142" spans="1:7" ht="15.6">
       <c r="A142" s="113"/>
       <c r="B142" s="116"/>
       <c r="C142" s="52">
@@ -4129,7 +4129,7 @@
       <c r="F171" s="57"/>
       <c r="G171" s="56"/>
     </row>
-    <row r="172" spans="1:7" ht="15.5">
+    <row r="172" spans="1:7" ht="15.6">
       <c r="A172" s="113"/>
       <c r="B172" s="116"/>
       <c r="C172" s="52">
@@ -5001,7 +5001,7 @@
       <c r="F229" s="68"/>
       <c r="G229" s="56"/>
     </row>
-    <row r="230" spans="1:7" ht="15.5">
+    <row r="230" spans="1:7" ht="15.6">
       <c r="A230" s="113"/>
       <c r="B230" s="116"/>
       <c r="C230" s="52">
@@ -5014,7 +5014,7 @@
       <c r="F230" s="68"/>
       <c r="G230" s="70"/>
     </row>
-    <row r="231" spans="1:7" ht="15.5">
+    <row r="231" spans="1:7" ht="15.6">
       <c r="A231" s="113"/>
       <c r="B231" s="116"/>
       <c r="C231" s="52">
@@ -5732,17 +5732,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="5.26953125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="7.7265625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="18.7265625" style="43" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" style="43" customWidth="1"/>
-    <col min="5" max="5" width="18.81640625" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="9.1796875" style="4"/>
+    <col min="1" max="1" width="5.21875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="7.77734375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.77734375" style="43" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" style="43" customWidth="1"/>
+    <col min="5" max="5" width="18.77734375" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="9.21875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="47.5" thickBot="1">
+    <row r="1" spans="1:5" ht="47.4" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5759,7 +5759,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.5" customHeight="1">
+    <row r="2" spans="1:5" ht="15.45" customHeight="1">
       <c r="A2" s="125" t="s">
         <v>5</v>
       </c>
@@ -5777,7 +5777,7 @@
       <c r="D3" s="12"/>
       <c r="E3" s="13"/>
     </row>
-    <row r="4" spans="1:5" ht="15.5" customHeight="1">
+    <row r="4" spans="1:5" ht="15.45" customHeight="1">
       <c r="A4" s="126"/>
       <c r="B4" s="118" t="s">
         <v>7</v>
@@ -5797,7 +5797,7 @@
       <c r="D5" s="21"/>
       <c r="E5" s="22"/>
     </row>
-    <row r="6" spans="1:5" ht="15.5" customHeight="1">
+    <row r="6" spans="1:5" ht="15.45" customHeight="1">
       <c r="A6" s="126"/>
       <c r="B6" s="118" t="s">
         <v>9</v>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="E7" s="22"/>
     </row>
-    <row r="8" spans="1:5" ht="15.5" customHeight="1">
+    <row r="8" spans="1:5" ht="15.45" customHeight="1">
       <c r="A8" s="126"/>
       <c r="B8" s="118" t="s">
         <v>11</v>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="E10" s="30"/>
     </row>
-    <row r="11" spans="1:5" ht="53" customHeight="1">
+    <row r="11" spans="1:5" ht="52.95" customHeight="1">
       <c r="A11" s="126"/>
       <c r="B11" s="124"/>
       <c r="C11" s="20" t="s">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="E11" s="24"/>
     </row>
-    <row r="12" spans="1:5" ht="15.5" customHeight="1">
+    <row r="12" spans="1:5" ht="15.45" customHeight="1">
       <c r="A12" s="126"/>
       <c r="B12" s="118" t="s">
         <v>15</v>
@@ -5876,7 +5876,7 @@
       <c r="D12" s="18"/>
       <c r="E12" s="25"/>
     </row>
-    <row r="13" spans="1:5" ht="16" customHeight="1">
+    <row r="13" spans="1:5" ht="16.05" customHeight="1">
       <c r="A13" s="126"/>
       <c r="B13" s="124"/>
       <c r="C13" s="20" t="s">
@@ -5885,7 +5885,7 @@
       <c r="D13" s="21"/>
       <c r="E13" s="24"/>
     </row>
-    <row r="14" spans="1:5" ht="15.5" customHeight="1">
+    <row r="14" spans="1:5" ht="15.45" customHeight="1">
       <c r="A14" s="121"/>
       <c r="B14" s="118" t="s">
         <v>18</v>
@@ -5896,7 +5896,7 @@
       <c r="D14" s="19"/>
       <c r="E14" s="13"/>
     </row>
-    <row r="15" spans="1:5" ht="15.5" customHeight="1">
+    <row r="15" spans="1:5" ht="15.45" customHeight="1">
       <c r="A15" s="121"/>
       <c r="B15" s="124"/>
       <c r="C15" s="20" t="s">
@@ -5905,7 +5905,7 @@
       <c r="D15" s="14"/>
       <c r="E15" s="22"/>
     </row>
-    <row r="16" spans="1:5" ht="15.5" customHeight="1">
+    <row r="16" spans="1:5" ht="15.45" customHeight="1">
       <c r="A16" s="111"/>
       <c r="B16" s="118" t="s">
         <v>19</v>
@@ -5914,14 +5914,14 @@
       <c r="D16" s="29"/>
       <c r="E16" s="30"/>
     </row>
-    <row r="17" spans="1:5" ht="16" thickBot="1">
+    <row r="17" spans="1:5" ht="16.2" thickBot="1">
       <c r="A17" s="111"/>
       <c r="B17" s="119"/>
       <c r="C17" s="36"/>
       <c r="D17" s="36"/>
       <c r="E17" s="22"/>
     </row>
-    <row r="18" spans="1:5" ht="15.5" customHeight="1">
+    <row r="18" spans="1:5" ht="15.45" customHeight="1">
       <c r="A18" s="125" t="s">
         <v>20</v>
       </c>
@@ -5939,7 +5939,7 @@
       <c r="D19" s="21"/>
       <c r="E19" s="13"/>
     </row>
-    <row r="20" spans="1:5" ht="15.5" customHeight="1">
+    <row r="20" spans="1:5" ht="15.45" customHeight="1">
       <c r="A20" s="126"/>
       <c r="B20" s="118" t="s">
         <v>7</v>
@@ -5959,7 +5959,7 @@
       <c r="D21" s="20"/>
       <c r="E21" s="24"/>
     </row>
-    <row r="22" spans="1:5" ht="15.5" customHeight="1">
+    <row r="22" spans="1:5" ht="15.45" customHeight="1">
       <c r="A22" s="126"/>
       <c r="B22" s="118" t="s">
         <v>9</v>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="E23" s="31"/>
     </row>
-    <row r="24" spans="1:5" ht="15.5" customHeight="1">
+    <row r="24" spans="1:5" ht="15.45" customHeight="1">
       <c r="A24" s="126"/>
       <c r="B24" s="118" t="s">
         <v>11</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="E25" s="31"/>
     </row>
-    <row r="26" spans="1:5" ht="15.5" customHeight="1">
+    <row r="26" spans="1:5" ht="15.45" customHeight="1">
       <c r="A26" s="126"/>
       <c r="B26" s="118" t="s">
         <v>13</v>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="E27" s="24"/>
     </row>
-    <row r="28" spans="1:5" ht="15.5" customHeight="1">
+    <row r="28" spans="1:5" ht="15.45" customHeight="1">
       <c r="A28" s="126"/>
       <c r="B28" s="118" t="s">
         <v>15</v>
@@ -6051,7 +6051,7 @@
       <c r="D29" s="33"/>
       <c r="E29" s="22"/>
     </row>
-    <row r="30" spans="1:5" ht="15.5" customHeight="1">
+    <row r="30" spans="1:5" ht="15.45" customHeight="1">
       <c r="A30" s="126"/>
       <c r="B30" s="118" t="s">
         <v>18</v>
@@ -6071,7 +6071,7 @@
       <c r="D31" s="20"/>
       <c r="E31" s="13"/>
     </row>
-    <row r="32" spans="1:5" ht="15.5" customHeight="1">
+    <row r="32" spans="1:5" ht="15.45" customHeight="1">
       <c r="A32" s="126"/>
       <c r="B32" s="118" t="s">
         <v>19</v>
@@ -6080,14 +6080,14 @@
       <c r="D32" s="19"/>
       <c r="E32" s="17"/>
     </row>
-    <row r="33" spans="1:5" ht="16" thickBot="1">
+    <row r="33" spans="1:5" ht="16.2" thickBot="1">
       <c r="A33" s="127"/>
       <c r="B33" s="119"/>
       <c r="C33" s="26"/>
       <c r="D33" s="34"/>
       <c r="E33" s="13"/>
     </row>
-    <row r="34" spans="1:5" ht="15.5" customHeight="1">
+    <row r="34" spans="1:5" ht="15.45" customHeight="1">
       <c r="A34" s="125" t="s">
         <v>21</v>
       </c>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="E41" s="13"/>
     </row>
-    <row r="42" spans="1:5" ht="15.5" customHeight="1">
+    <row r="42" spans="1:5" ht="15.45" customHeight="1">
       <c r="A42" s="126"/>
       <c r="B42" s="118" t="s">
         <v>13</v>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="E43" s="24"/>
     </row>
-    <row r="44" spans="1:5" ht="15.5" customHeight="1">
+    <row r="44" spans="1:5" ht="15.45" customHeight="1">
       <c r="A44" s="126"/>
       <c r="B44" s="118" t="s">
         <v>15</v>
@@ -6221,7 +6221,7 @@
       <c r="D45" s="20"/>
       <c r="E45" s="22"/>
     </row>
-    <row r="46" spans="1:5" ht="15.5" customHeight="1">
+    <row r="46" spans="1:5" ht="15.45" customHeight="1">
       <c r="A46" s="126"/>
       <c r="B46" s="118" t="s">
         <v>18</v>
@@ -6232,7 +6232,7 @@
       <c r="D46" s="29"/>
       <c r="E46" s="17"/>
     </row>
-    <row r="47" spans="1:5" ht="15.5" customHeight="1">
+    <row r="47" spans="1:5" ht="15.45" customHeight="1">
       <c r="A47" s="126"/>
       <c r="B47" s="124"/>
       <c r="C47" s="20" t="s">
@@ -6241,7 +6241,7 @@
       <c r="D47" s="20"/>
       <c r="E47" s="22"/>
     </row>
-    <row r="48" spans="1:5" ht="15.5" customHeight="1">
+    <row r="48" spans="1:5" ht="15.45" customHeight="1">
       <c r="A48" s="126"/>
       <c r="B48" s="118" t="s">
         <v>19</v>
@@ -6250,14 +6250,14 @@
       <c r="D48" s="29"/>
       <c r="E48" s="17"/>
     </row>
-    <row r="49" spans="1:5" ht="16" thickBot="1">
+    <row r="49" spans="1:5" ht="16.2" thickBot="1">
       <c r="A49" s="127"/>
       <c r="B49" s="119"/>
       <c r="C49" s="36"/>
       <c r="D49" s="36"/>
       <c r="E49" s="22"/>
     </row>
-    <row r="50" spans="1:5" ht="15.5" customHeight="1">
+    <row r="50" spans="1:5" ht="15.45" customHeight="1">
       <c r="A50" s="125" t="s">
         <v>24</v>
       </c>
@@ -6275,7 +6275,7 @@
       <c r="D51" s="14"/>
       <c r="E51" s="22"/>
     </row>
-    <row r="52" spans="1:5" ht="15.5" customHeight="1">
+    <row r="52" spans="1:5" ht="15.45" customHeight="1">
       <c r="A52" s="126"/>
       <c r="B52" s="118" t="s">
         <v>7</v>
@@ -6295,7 +6295,7 @@
       <c r="D53" s="12"/>
       <c r="E53" s="22"/>
     </row>
-    <row r="54" spans="1:5" ht="15.5" customHeight="1">
+    <row r="54" spans="1:5" ht="15.45" customHeight="1">
       <c r="A54" s="126"/>
       <c r="B54" s="118" t="s">
         <v>9</v>
@@ -6317,7 +6317,7 @@
       <c r="D55" s="12"/>
       <c r="E55" s="22"/>
     </row>
-    <row r="56" spans="1:5" ht="15.5" customHeight="1">
+    <row r="56" spans="1:5" ht="15.45" customHeight="1">
       <c r="A56" s="126"/>
       <c r="B56" s="118" t="s">
         <v>11</v>
@@ -6383,7 +6383,7 @@
       <c r="D61" s="20"/>
       <c r="E61" s="22"/>
     </row>
-    <row r="62" spans="1:5" ht="15.5" customHeight="1">
+    <row r="62" spans="1:5" ht="15.45" customHeight="1">
       <c r="A62" s="126"/>
       <c r="B62" s="118" t="s">
         <v>18</v>
@@ -6394,7 +6394,7 @@
       <c r="D62" s="15"/>
       <c r="E62" s="17"/>
     </row>
-    <row r="63" spans="1:5" ht="15.5" customHeight="1">
+    <row r="63" spans="1:5" ht="15.45" customHeight="1">
       <c r="A63" s="126"/>
       <c r="B63" s="124"/>
       <c r="C63" s="20" t="s">
@@ -6403,7 +6403,7 @@
       <c r="D63" s="20"/>
       <c r="E63" s="22"/>
     </row>
-    <row r="64" spans="1:5" ht="15.5" customHeight="1">
+    <row r="64" spans="1:5" ht="15.45" customHeight="1">
       <c r="A64" s="126"/>
       <c r="B64" s="118" t="s">
         <v>19</v>
@@ -6412,14 +6412,14 @@
       <c r="D64" s="16"/>
       <c r="E64" s="17"/>
     </row>
-    <row r="65" spans="1:5" ht="16" thickBot="1">
+    <row r="65" spans="1:5" ht="16.2" thickBot="1">
       <c r="A65" s="127"/>
       <c r="B65" s="119"/>
       <c r="C65" s="36"/>
       <c r="D65" s="36"/>
       <c r="E65" s="22"/>
     </row>
-    <row r="66" spans="1:5" ht="15.5" customHeight="1">
+    <row r="66" spans="1:5" ht="15.45" customHeight="1">
       <c r="A66" s="125" t="s">
         <v>26</v>
       </c>
@@ -6437,7 +6437,7 @@
       <c r="D67" s="35"/>
       <c r="E67" s="22"/>
     </row>
-    <row r="68" spans="1:5" ht="15.5" customHeight="1">
+    <row r="68" spans="1:5" ht="15.45" customHeight="1">
       <c r="A68" s="126"/>
       <c r="B68" s="118" t="s">
         <v>7</v>
@@ -6457,7 +6457,7 @@
       <c r="D69" s="20"/>
       <c r="E69" s="24"/>
     </row>
-    <row r="70" spans="1:5" ht="15.5" customHeight="1">
+    <row r="70" spans="1:5" ht="15.45" customHeight="1">
       <c r="A70" s="126"/>
       <c r="B70" s="118" t="s">
         <v>9</v>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="E71" s="22"/>
     </row>
-    <row r="72" spans="1:5" ht="15.5" customHeight="1">
+    <row r="72" spans="1:5" ht="15.45" customHeight="1">
       <c r="A72" s="126"/>
       <c r="B72" s="118" t="s">
         <v>11</v>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="E73" s="22"/>
     </row>
-    <row r="74" spans="1:5" ht="15.5" customHeight="1">
+    <row r="74" spans="1:5" ht="15.45" customHeight="1">
       <c r="A74" s="126"/>
       <c r="B74" s="118" t="s">
         <v>13</v>
@@ -6525,7 +6525,7 @@
       <c r="D75" s="20"/>
       <c r="E75" s="24"/>
     </row>
-    <row r="76" spans="1:5" ht="15.5" customHeight="1">
+    <row r="76" spans="1:5" ht="15.45" customHeight="1">
       <c r="A76" s="126"/>
       <c r="B76" s="118" t="s">
         <v>15</v>
@@ -6545,7 +6545,7 @@
       <c r="D77" s="35"/>
       <c r="E77" s="22"/>
     </row>
-    <row r="78" spans="1:5" ht="15.5" customHeight="1">
+    <row r="78" spans="1:5" ht="15.45" customHeight="1">
       <c r="A78" s="126"/>
       <c r="B78" s="118" t="s">
         <v>18</v>
@@ -6556,7 +6556,7 @@
       <c r="D78" s="29"/>
       <c r="E78" s="17"/>
     </row>
-    <row r="79" spans="1:5" ht="15.5" customHeight="1">
+    <row r="79" spans="1:5" ht="15.45" customHeight="1">
       <c r="A79" s="126"/>
       <c r="B79" s="124"/>
       <c r="C79" s="20" t="s">
@@ -6565,7 +6565,7 @@
       <c r="D79" s="35"/>
       <c r="E79" s="22"/>
     </row>
-    <row r="80" spans="1:5" ht="15.5" customHeight="1">
+    <row r="80" spans="1:5" ht="15.45" customHeight="1">
       <c r="A80" s="126"/>
       <c r="B80" s="118" t="s">
         <v>19</v>
@@ -6574,14 +6574,14 @@
       <c r="D80" s="29"/>
       <c r="E80" s="17"/>
     </row>
-    <row r="81" spans="1:5" ht="16" thickBot="1">
+    <row r="81" spans="1:5" ht="16.2" thickBot="1">
       <c r="A81" s="127"/>
       <c r="B81" s="119"/>
       <c r="C81" s="36"/>
       <c r="D81" s="35"/>
       <c r="E81" s="40"/>
     </row>
-    <row r="82" spans="1:5" ht="15.5" customHeight="1">
+    <row r="82" spans="1:5" ht="15.45" customHeight="1">
       <c r="A82" s="120" t="s">
         <v>27</v>
       </c>
@@ -6635,7 +6635,7 @@
       <c r="D87" s="12"/>
       <c r="E87" s="22"/>
     </row>
-    <row r="88" spans="1:5" ht="15.5" customHeight="1">
+    <row r="88" spans="1:5" ht="15.45" customHeight="1">
       <c r="A88" s="121"/>
       <c r="B88" s="118" t="s">
         <v>11</v>
@@ -6655,7 +6655,7 @@
       <c r="D89" s="12"/>
       <c r="E89" s="22"/>
     </row>
-    <row r="90" spans="1:5" ht="15.5" customHeight="1">
+    <row r="90" spans="1:5" ht="15.45" customHeight="1">
       <c r="A90" s="121"/>
       <c r="B90" s="118" t="s">
         <v>13</v>
@@ -6673,7 +6673,7 @@
       <c r="D91" s="14"/>
       <c r="E91" s="22"/>
     </row>
-    <row r="92" spans="1:5" ht="15.5" customHeight="1">
+    <row r="92" spans="1:5" ht="15.45" customHeight="1">
       <c r="A92" s="121"/>
       <c r="B92" s="118" t="s">
         <v>15</v>
@@ -6682,7 +6682,7 @@
       <c r="D92" s="19"/>
       <c r="E92" s="17"/>
     </row>
-    <row r="93" spans="1:5" ht="16" thickBot="1">
+    <row r="93" spans="1:5" ht="16.2" thickBot="1">
       <c r="A93" s="122"/>
       <c r="B93" s="119"/>
       <c r="C93" s="26"/>
